--- a/data/trans_camb/IP21B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Clase-trans_camb.xlsx
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 82,36</t>
+          <t>-35,22; 82,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 82,24</t>
+          <t>-35,31; 82,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 83,63</t>
+          <t>-34,86; 82,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 69,33</t>
+          <t>-14,47; 78,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 64,75</t>
+          <t>-7,86; 65,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 69,76</t>
+          <t>-7,24; 74,2</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 91,11</t>
+          <t>0,0; 84,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,32; 0,0</t>
+          <t>-36,0; 0,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 0,0</t>
+          <t>-43,55; 0,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 72,59</t>
+          <t>-17,77; 74,15</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 54,35</t>
+          <t>-36,49; 54,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 0,0</t>
+          <t>-63,71; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 33,02</t>
+          <t>-35,62; 42,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 0,0</t>
+          <t>-60,47; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 79,51</t>
+          <t>-34,16; 80,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 28,1</t>
+          <t>-20,82; 28,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 72,57</t>
+          <t>-11,77; 70,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 0,0</t>
+          <t>-39,35; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 43,81</t>
+          <t>5,8; 45,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,36</t>
+          <t>0,0; 83,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,51</t>
+          <t>0,0; 72,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 29,17</t>
+          <t>1,24; 29,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 59,89</t>
+          <t>4,12; 61,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 45,99</t>
+          <t>-8,28; 44,38</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1541,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 52,6</t>
+          <t>-36,07; 52,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 57,24</t>
+          <t>-34,16; 57,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 88,28</t>
+          <t>-35,4; 82,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,68</t>
+          <t>0,0; 51,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,12; 82,08</t>
+          <t>12,29; 82,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 35,55</t>
+          <t>-9,77; 35,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,25; 60,01</t>
+          <t>5,2; 60,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 55,01</t>
+          <t>-13,43; 51,34</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,37</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 29,79</t>
+          <t>-46,9; 30,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 34,13</t>
+          <t>-21,72; 34,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 67,42</t>
+          <t>-20,65; 67,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 22,32</t>
+          <t>-3,74; 24,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,86; 38,89</t>
+          <t>2,99; 37,48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 47,64</t>
+          <t>-0,52; 50,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 23,88</t>
+          <t>-6,36; 21,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 29,5</t>
+          <t>-4,01; 30,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 44,54</t>
+          <t>-6,45; 40,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 19,5</t>
+          <t>-1,28; 18,49</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,12; 26,43</t>
+          <t>4,12; 28,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,47; 34,11</t>
+          <t>2,5; 36,63</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-74,73; —</t>
+          <t>-66,46; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,85; —</t>
+          <t>-25,8; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 491,78</t>
+          <t>-44,21; 432,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 643,36</t>
+          <t>-47,22; 590,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 991,76</t>
+          <t>-61,15; 807,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 406,1</t>
+          <t>-14,14; 522,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,9; 570,43</t>
+          <t>19,63; 669,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 735,49</t>
+          <t>2,31; 742,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Clase-trans_camb.xlsx
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 82,4</t>
+          <t>-35,72; 82,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 82,52</t>
+          <t>-34,78; 83,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 78,13</t>
+          <t>-15,01; 64,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 65,18</t>
+          <t>-8,94; 63,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 74,2</t>
+          <t>-7,26; 76,85</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 0,0</t>
+          <t>-42,69; 0,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 0,0</t>
+          <t>-40,88; 0,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 74,15</t>
+          <t>-18,14; 68,73</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 54,45</t>
+          <t>-36,53; 55,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 0,0</t>
+          <t>-63,93; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,62; 42,53</t>
+          <t>-34,4; 42,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,47; 0,0</t>
+          <t>-56,5; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 80,39</t>
+          <t>-34,53; 88,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 28,67</t>
+          <t>-24,42; 28,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 70,84</t>
+          <t>-13,34; 68,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 0,0</t>
+          <t>-44,93; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 45,09</t>
+          <t>5,78; 49,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,5</t>
+          <t>0,0; 68,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,2</t>
+          <t>0,0; 64,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 29,16</t>
+          <t>0,04; 29,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 61,44</t>
+          <t>4,22; 60,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 44,38</t>
+          <t>-8,29; 49,09</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1541,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 52,55</t>
+          <t>-35,46; 52,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 57,71</t>
+          <t>-32,74; 57,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 82,88</t>
+          <t>-35,33; 86,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,49</t>
+          <t>0,0; 55,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,29; 82,12</t>
+          <t>12,02; 82,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 35,39</t>
+          <t>-9,3; 35,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 60,64</t>
+          <t>5,85; 60,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 51,34</t>
+          <t>-13,39; 53,53</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 30,02</t>
+          <t>-46,9; 29,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 34,28</t>
+          <t>-21,15; 33,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 67,42</t>
+          <t>-20,57; 67,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 24,54</t>
+          <t>-3,73; 21,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,99; 37,48</t>
+          <t>3,68; 39,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 50,44</t>
+          <t>-2,18; 47,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 21,5</t>
+          <t>-6,85; 22,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 30,26</t>
+          <t>-6,85; 28,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 40,94</t>
+          <t>-5,48; 43,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 18,49</t>
+          <t>-2,09; 18,85</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,12; 28,41</t>
+          <t>1,61; 26,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,5; 36,63</t>
+          <t>1,1; 35,98</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-66,46; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,8; —</t>
+          <t>-23,0; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,21; 432,01</t>
+          <t>-50,36; 456,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 590,29</t>
+          <t>-52,73; 618,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 807,9</t>
+          <t>-58,63; 859,42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 522,36</t>
+          <t>-22,8; 392,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>19,63; 669,36</t>
+          <t>1,62; 550,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2,31; 742,82</t>
+          <t>-21,72; 705,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>27,61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,33</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>33,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26,84</t>
+          <t>26,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,36; 82,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>-35,76; 82,24</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-34,73; 83,03</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-35,22; 82,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-35,72; 82,37</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,78; 83,48</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 64,13</t>
+          <t>-14,61; 69,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 63,59</t>
+          <t>-7,66; 64,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 76,85</t>
+          <t>-7,65; 67,71</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92,71%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>69,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>69,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>103,2%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>189,63%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>363,08%</t>
+          <t>364,38%</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-25,18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-25,18</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-25,18</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-25,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-25,18</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-25,18</t>
+          <t>35,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,95</t>
+          <t>19,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,1; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,1; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-77,1; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,1; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 86,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 0,0</t>
+          <t>-36,32; 0,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 0,0</t>
+          <t>-41,81; 0,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 68,73</t>
+          <t>-18,0; 74,73</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>188,3%</t>
+          <t>212,5%</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-24,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75,38</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-24,62</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>75,38</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-0,39</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,78</t>
+          <t>17,11</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,44; 54,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,72; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 55,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,93; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 42,59</t>
+          <t>-34,76; 33,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 0,0</t>
+          <t>-57,21; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 88,26</t>
+          <t>-43,42; 79,53</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>32,71%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>306,11%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32,71%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-1,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>306,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-1,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33,4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18,57</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>24,09</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-9,99</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,89</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>14,65</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>9,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 28,4</t>
+          <t>5,59; 43,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 68,99</t>
+          <t>0,0; 83,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 0,0</t>
+          <t>0,0; 80,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 49,32</t>
+          <t>-20,86; 28,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,89</t>
+          <t>-11,31; 72,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,75</t>
+          <t>-39,32; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 29,38</t>
+          <t>-0,43; 29,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 60,39</t>
+          <t>4,33; 59,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 49,09</t>
+          <t>-8,18; 50,68</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>85,58%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>241,2%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>352,5%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199,45%</t>
+          <t>235,99%</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17,95</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>41,33</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>18,39</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20,06</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17,95</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>41,33</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>22,34</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>11,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 52,61</t>
+          <t>0,0; 49,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 57,38</t>
+          <t>12,12; 82,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 86,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,75</t>
+          <t>-35,85; 52,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 82,81</t>
+          <t>-32,67; 57,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,33; 93,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 35,11</t>
+          <t>-10,05; 35,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 60,41</t>
+          <t>4,25; 60,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 53,53</t>
+          <t>-13,42; 59,44</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>109,43%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>119,4%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>132,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>135,83%</t>
+          <t>172,12%</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-15,08</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>84,92</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>31,88</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-15,08</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>84,92</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-46,68; 29,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 29,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 81,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 33,76</t>
+          <t>-21,72; 34,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 67,42</t>
+          <t>-20,6; 67,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-2,85%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>563,07%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-2,85%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>563,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8,28</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10,34</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>15,59</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>8,34</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>19,61</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>19,08</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>8,28</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,34</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,8</t>
+          <t>21,42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,65</t>
+          <t>18,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 21,48</t>
+          <t>-4,82; 23,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,68; 39,35</t>
+          <t>-5,42; 29,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 47,58</t>
+          <t>-5,17; 47,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 22,81</t>
+          <t>-3,46; 22,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 28,84</t>
+          <t>3,86; 38,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 43,75</t>
+          <t>0,03; 50,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 18,85</t>
+          <t>-0,61; 19,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,61; 26,46</t>
+          <t>2,12; 26,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,1; 35,98</t>
+          <t>2,32; 36,66</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>76,05%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>143,25%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>158,52%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>372,8%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>362,72%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>76,05%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>135,93%</t>
+          <t>407,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>196,64%</t>
+          <t>213,82%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-37,19; 491,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,0; —</t>
+          <t>-49,41; 643,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,4; 1082,85</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 456,07</t>
+          <t>-74,73; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 618,38</t>
+          <t>-13,85; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-58,63; 859,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 392,75</t>
+          <t>-18,31; 406,1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,62; 550,88</t>
+          <t>9,9; 570,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 705,14</t>
+          <t>-2,46; 811,59</t>
         </is>
       </c>
     </row>
